--- a/Dienstplan-Vorlage-Wohngruppe.xlsx
+++ b/Dienstplan-Vorlage-Wohngruppe.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mikeweinert/Developer/dienstplan-app/hochladen/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="11_FB47EC0023607736170B12F94D2C069B257FC5EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="29400" windowHeight="19120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -243,7 +238,7 @@
     <t>Mehr als das hier geht in Excel kaum noch — und ein paar Dinge gehen gar nicht: das vollständige Arbeitszeitgesetz prüfen (Arbeitstage am Stück, Nachtdienst-Kontingente je Person — die violette Warnung sieht nur den häufigsten Fall), Nachtbereitschaft anteilig aufs Zeitkonto rechnen, Zeitkonten und Resturlaub über den Monatswechsel mitnehmen, den Plan automatisch und fair nach Stunden-Soll füllen, Anträge und Diensttausch des Teams verwalten oder einen sauberen Aushang fürs Brett erzeugen.</t>
   </si>
   <si>
-    <t>Wer das braucht: Für genau diese Lücken gibt es die Anwendung „Dienstplan Jugendhilfe“ — läuft auf dem Rechner im Haus, ohne Cloud und ohne Konto, 179 € einmalig. Alles Weitere auf dienstplan-jugendhilfe.de</t>
+    <t>Wer das braucht: Für genau diese Lücken gibt es die Anwendung „Dienstplan Jugendhilfe“ — läuft auf dem Rechner im Haus, ohne Cloud und ohne Konto, kostenlos und ohne Abo. Alles Weitere auf dienstplan-jugendhilfe.de</t>
   </si>
   <si>
     <t>Diese Vorlage ist frei verwendbar, auch verändert und weitergegeben.</t>
